--- a/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11921" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11921" uniqueCount="792">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T13:57:28+00:00</t>
+    <t>2026-01-29T11:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1136,7 +1136,7 @@
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
@@ -1404,9 +1404,6 @@
   <si>
     <t xml:space="preserve">profile:resolve()}
 </t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Composition.section:sectionMedications.entry:medicationStatement</t>
@@ -7794,7 +7791,7 @@
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
         <v>363</v>
@@ -10735,10 +10732,10 @@
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>413</v>
@@ -10773,13 +10770,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -10801,7 +10798,7 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>414</v>
@@ -10892,13 +10889,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -10920,7 +10917,7 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>414</v>
@@ -11011,13 +11008,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
@@ -11039,7 +11036,7 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>414</v>
@@ -11130,13 +11127,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
@@ -11158,7 +11155,7 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>414</v>
@@ -11249,13 +11246,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>79</v>
@@ -11277,7 +11274,7 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>414</v>
@@ -11368,7 +11365,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>420</v>
@@ -11487,7 +11484,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>428</v>
@@ -11604,13 +11601,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
@@ -11721,7 +11718,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>367</v>
@@ -11836,7 +11833,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>368</v>
@@ -11953,7 +11950,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>369</v>
@@ -12072,7 +12069,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>370</v>
@@ -12191,7 +12188,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>376</v>
@@ -12239,7 +12236,7 @@
         <v>79</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>79</v>
@@ -12310,7 +12307,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>383</v>
@@ -12427,7 +12424,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>386</v>
@@ -12544,7 +12541,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>391</v>
@@ -12661,7 +12658,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>397</v>
@@ -12780,7 +12777,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>405</v>
@@ -12899,7 +12896,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>413</v>
@@ -12925,7 +12922,7 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>414</v>
@@ -12976,10 +12973,10 @@
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>413</v>
@@ -13014,13 +13011,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
@@ -13042,7 +13039,7 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>414</v>
@@ -13133,13 +13130,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13161,7 +13158,7 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>414</v>
@@ -13252,7 +13249,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>420</v>
@@ -13371,7 +13368,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>428</v>
@@ -13488,13 +13485,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>79</v>
@@ -13605,7 +13602,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>367</v>
@@ -13720,7 +13717,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>368</v>
@@ -13837,7 +13834,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>369</v>
@@ -13956,7 +13953,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>370</v>
@@ -14075,7 +14072,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>376</v>
@@ -14123,7 +14120,7 @@
         <v>79</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>79</v>
@@ -14194,7 +14191,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>383</v>
@@ -14311,7 +14308,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>386</v>
@@ -14428,7 +14425,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>391</v>
@@ -14545,7 +14542,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>397</v>
@@ -14664,7 +14661,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>405</v>
@@ -14783,7 +14780,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>413</v>
@@ -14809,7 +14806,7 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>414</v>
@@ -14860,10 +14857,10 @@
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>413</v>
@@ -14898,13 +14895,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14926,7 +14923,7 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>414</v>
@@ -15017,13 +15014,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -15045,7 +15042,7 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>414</v>
@@ -15136,7 +15133,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>420</v>
@@ -15255,7 +15252,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>428</v>
@@ -15372,13 +15369,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>79</v>
@@ -15469,7 +15466,7 @@
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -15489,7 +15486,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>367</v>
@@ -15604,7 +15601,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>368</v>
@@ -15721,7 +15718,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>369</v>
@@ -15840,7 +15837,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>370</v>
@@ -15959,7 +15956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>376</v>
@@ -16007,7 +16004,7 @@
         <v>79</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>79</v>
@@ -16078,7 +16075,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>383</v>
@@ -16195,7 +16192,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>386</v>
@@ -16312,7 +16309,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>391</v>
@@ -16429,7 +16426,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>397</v>
@@ -16548,7 +16545,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>405</v>
@@ -16667,7 +16664,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>413</v>
@@ -16693,7 +16690,7 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>414</v>
@@ -16744,10 +16741,10 @@
       </c>
       <c r="AC118" s="2"/>
       <c r="AD118" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF118" t="s" s="2">
         <v>413</v>
@@ -16782,13 +16779,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>79</v>
@@ -16810,7 +16807,7 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>414</v>
@@ -16901,13 +16898,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>79</v>
@@ -16929,7 +16926,7 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>414</v>
@@ -17020,7 +17017,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>420</v>
@@ -17139,7 +17136,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>428</v>
@@ -17256,13 +17253,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>79</v>
@@ -17353,7 +17350,7 @@
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
@@ -17373,7 +17370,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>367</v>
@@ -17488,7 +17485,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>368</v>
@@ -17605,7 +17602,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>369</v>
@@ -17724,7 +17721,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>370</v>
@@ -17843,7 +17840,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>376</v>
@@ -17891,7 +17888,7 @@
         <v>79</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>79</v>
@@ -17962,7 +17959,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>383</v>
@@ -18079,7 +18076,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>386</v>
@@ -18196,7 +18193,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>391</v>
@@ -18313,7 +18310,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>397</v>
@@ -18432,7 +18429,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>405</v>
@@ -18551,7 +18548,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>413</v>
@@ -18577,7 +18574,7 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>414</v>
@@ -18628,10 +18625,10 @@
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF134" t="s" s="2">
         <v>413</v>
@@ -18666,13 +18663,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>79</v>
@@ -18694,7 +18691,7 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>414</v>
@@ -18785,13 +18782,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>79</v>
@@ -18813,7 +18810,7 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>414</v>
@@ -18904,7 +18901,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>420</v>
@@ -19023,7 +19020,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>428</v>
@@ -19140,13 +19137,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>79</v>
@@ -19257,7 +19254,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>367</v>
@@ -19372,7 +19369,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>368</v>
@@ -19489,7 +19486,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>369</v>
@@ -19608,7 +19605,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>370</v>
@@ -19727,7 +19724,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>376</v>
@@ -19775,7 +19772,7 @@
         <v>79</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>79</v>
@@ -19846,7 +19843,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>383</v>
@@ -19963,7 +19960,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>386</v>
@@ -20080,7 +20077,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>391</v>
@@ -20197,7 +20194,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>397</v>
@@ -20316,7 +20313,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>405</v>
@@ -20435,7 +20432,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>413</v>
@@ -20461,7 +20458,7 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>414</v>
@@ -20512,10 +20509,10 @@
       </c>
       <c r="AC150" s="2"/>
       <c r="AD150" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF150" t="s" s="2">
         <v>413</v>
@@ -20550,13 +20547,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>79</v>
@@ -20578,7 +20575,7 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>414</v>
@@ -20669,13 +20666,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -20697,7 +20694,7 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>414</v>
@@ -20788,7 +20785,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>420</v>
@@ -20907,7 +20904,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>428</v>
@@ -21024,13 +21021,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
@@ -21141,7 +21138,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>367</v>
@@ -21256,7 +21253,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>368</v>
@@ -21373,7 +21370,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>369</v>
@@ -21492,7 +21489,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>370</v>
@@ -21611,7 +21608,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>376</v>
@@ -21659,7 +21656,7 @@
         <v>79</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>79</v>
@@ -21730,7 +21727,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>383</v>
@@ -21847,7 +21844,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>386</v>
@@ -21964,7 +21961,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>391</v>
@@ -22081,7 +22078,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>397</v>
@@ -22200,7 +22197,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>405</v>
@@ -22319,7 +22316,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>413</v>
@@ -22345,7 +22342,7 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>414</v>
@@ -22392,11 +22389,11 @@
         <v>79</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AC166" s="2"/>
       <c r="AD166" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE166" t="s" s="2">
         <v>363</v>
@@ -22434,13 +22431,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>79</v>
@@ -22462,7 +22459,7 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L167" t="s" s="2">
         <v>414</v>
@@ -22553,13 +22550,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>79</v>
@@ -22581,7 +22578,7 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L168" t="s" s="2">
         <v>414</v>
@@ -22672,13 +22669,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>79</v>
@@ -22700,7 +22697,7 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>414</v>
@@ -22791,13 +22788,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>79</v>
@@ -22819,7 +22816,7 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L170" t="s" s="2">
         <v>414</v>
@@ -22910,7 +22907,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>420</v>
@@ -23029,7 +23026,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>428</v>
@@ -23146,13 +23143,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>79</v>
@@ -23263,7 +23260,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>367</v>
@@ -23378,7 +23375,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>368</v>
@@ -23495,7 +23492,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>369</v>
@@ -23614,7 +23611,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>370</v>
@@ -23733,7 +23730,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>376</v>
@@ -23781,7 +23778,7 @@
         <v>79</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>79</v>
@@ -23852,7 +23849,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>383</v>
@@ -23969,7 +23966,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>386</v>
@@ -24086,7 +24083,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>391</v>
@@ -24203,7 +24200,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>397</v>
@@ -24322,7 +24319,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>405</v>
@@ -24441,7 +24438,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>413</v>
@@ -24467,7 +24464,7 @@
         <v>79</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L184" t="s" s="2">
         <v>414</v>
@@ -24518,7 +24515,7 @@
       </c>
       <c r="AC184" s="2"/>
       <c r="AD184" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE184" t="s" s="2">
         <v>363</v>
@@ -24556,13 +24553,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>79</v>
@@ -24584,7 +24581,7 @@
         <v>79</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>414</v>
@@ -24675,13 +24672,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>79</v>
@@ -24703,7 +24700,7 @@
         <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>414</v>
@@ -24794,7 +24791,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>420</v>
@@ -24913,7 +24910,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>428</v>
@@ -25030,13 +25027,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>79</v>
@@ -25147,7 +25144,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>367</v>
@@ -25262,7 +25259,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>368</v>
@@ -25379,7 +25376,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>369</v>
@@ -25498,7 +25495,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>370</v>
@@ -25617,7 +25614,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>376</v>
@@ -25665,7 +25662,7 @@
         <v>79</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>79</v>
@@ -25736,7 +25733,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>383</v>
@@ -25853,7 +25850,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>386</v>
@@ -25970,7 +25967,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>391</v>
@@ -26087,7 +26084,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>397</v>
@@ -26206,7 +26203,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>405</v>
@@ -26325,7 +26322,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>413</v>
@@ -26351,7 +26348,7 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L200" t="s" s="2">
         <v>414</v>
@@ -26402,10 +26399,10 @@
       </c>
       <c r="AC200" s="2"/>
       <c r="AD200" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF200" t="s" s="2">
         <v>413</v>
@@ -26440,13 +26437,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>79</v>
@@ -26468,7 +26465,7 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L201" t="s" s="2">
         <v>414</v>
@@ -26559,13 +26556,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>79</v>
@@ -26587,7 +26584,7 @@
         <v>79</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L202" t="s" s="2">
         <v>414</v>
@@ -26678,7 +26675,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>420</v>
@@ -26797,7 +26794,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>428</v>
@@ -26914,13 +26911,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
@@ -27031,7 +27028,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>367</v>
@@ -27146,7 +27143,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>368</v>
@@ -27263,7 +27260,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>369</v>
@@ -27382,7 +27379,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>370</v>
@@ -27501,7 +27498,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>376</v>
@@ -27549,7 +27546,7 @@
         <v>79</v>
       </c>
       <c r="S210" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="T210" t="s" s="2">
         <v>79</v>
@@ -27620,7 +27617,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>383</v>
@@ -27737,7 +27734,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>386</v>
@@ -27854,7 +27851,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>391</v>
@@ -27971,7 +27968,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>397</v>
@@ -28090,7 +28087,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>405</v>
@@ -28209,7 +28206,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>413</v>
@@ -28235,7 +28232,7 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L216" t="s" s="2">
         <v>414</v>
@@ -28286,10 +28283,10 @@
       </c>
       <c r="AC216" s="2"/>
       <c r="AD216" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF216" t="s" s="2">
         <v>413</v>
@@ -28324,13 +28321,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>79</v>
@@ -28352,7 +28349,7 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L217" t="s" s="2">
         <v>414</v>
@@ -28443,13 +28440,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>79</v>
@@ -28471,7 +28468,7 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>414</v>
@@ -28562,13 +28559,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>79</v>
@@ -28590,7 +28587,7 @@
         <v>79</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L219" t="s" s="2">
         <v>414</v>
@@ -28681,7 +28678,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>420</v>
@@ -28800,7 +28797,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>428</v>
@@ -28917,13 +28914,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -29034,7 +29031,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>367</v>
@@ -29149,7 +29146,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>368</v>
@@ -29266,7 +29263,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>369</v>
@@ -29385,7 +29382,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>370</v>
@@ -29504,7 +29501,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>376</v>
@@ -29552,7 +29549,7 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="T227" t="s" s="2">
         <v>79</v>
@@ -29623,7 +29620,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>383</v>
@@ -29740,7 +29737,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>386</v>
@@ -29857,7 +29854,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>391</v>
@@ -29974,7 +29971,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>397</v>
@@ -30093,7 +30090,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>405</v>
@@ -30212,7 +30209,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>413</v>
@@ -30238,7 +30235,7 @@
         <v>79</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L233" t="s" s="2">
         <v>414</v>
@@ -30289,10 +30286,10 @@
       </c>
       <c r="AC233" s="2"/>
       <c r="AD233" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF233" t="s" s="2">
         <v>413</v>
@@ -30327,13 +30324,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D234" t="s" s="2">
         <v>79</v>
@@ -30355,7 +30352,7 @@
         <v>79</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L234" t="s" s="2">
         <v>414</v>
@@ -30446,13 +30443,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>79</v>
@@ -30474,7 +30471,7 @@
         <v>79</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L235" t="s" s="2">
         <v>414</v>
@@ -30565,13 +30562,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D236" t="s" s="2">
         <v>79</v>
@@ -30593,7 +30590,7 @@
         <v>79</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L236" t="s" s="2">
         <v>414</v>
@@ -30684,7 +30681,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>420</v>
@@ -30803,7 +30800,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>428</v>
@@ -30920,13 +30917,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>79</v>
@@ -31037,7 +31034,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>367</v>
@@ -31152,7 +31149,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>368</v>
@@ -31269,7 +31266,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>369</v>
@@ -31388,7 +31385,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>370</v>
@@ -31507,7 +31504,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>376</v>
@@ -31555,7 +31552,7 @@
         <v>79</v>
       </c>
       <c r="S244" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="T244" t="s" s="2">
         <v>79</v>
@@ -31626,7 +31623,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>383</v>
@@ -31743,7 +31740,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>386</v>
@@ -31860,7 +31857,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>391</v>
@@ -31977,7 +31974,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>397</v>
@@ -32096,7 +32093,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>405</v>
@@ -32215,7 +32212,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>413</v>
@@ -32241,7 +32238,7 @@
         <v>79</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L250" t="s" s="2">
         <v>414</v>
@@ -32292,7 +32289,7 @@
       </c>
       <c r="AC250" s="2"/>
       <c r="AD250" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE250" t="s" s="2">
         <v>363</v>
@@ -32330,13 +32327,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D251" t="s" s="2">
         <v>79</v>
@@ -32358,7 +32355,7 @@
         <v>79</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L251" t="s" s="2">
         <v>414</v>
@@ -32449,13 +32446,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>79</v>
@@ -32477,7 +32474,7 @@
         <v>79</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L252" t="s" s="2">
         <v>414</v>
@@ -32568,13 +32565,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D253" t="s" s="2">
         <v>79</v>
@@ -32596,7 +32593,7 @@
         <v>79</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L253" t="s" s="2">
         <v>414</v>
@@ -32687,7 +32684,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>420</v>
@@ -32806,7 +32803,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>428</v>
@@ -32923,13 +32920,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>79</v>
@@ -33040,7 +33037,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>367</v>
@@ -33155,7 +33152,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>368</v>
@@ -33272,7 +33269,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>369</v>
@@ -33391,7 +33388,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>370</v>
@@ -33510,7 +33507,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>376</v>
@@ -33558,7 +33555,7 @@
         <v>79</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>79</v>
@@ -33629,7 +33626,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>383</v>
@@ -33746,7 +33743,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>386</v>
@@ -33863,7 +33860,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>391</v>
@@ -33980,7 +33977,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>397</v>
@@ -34099,7 +34096,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>405</v>
@@ -34218,7 +34215,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>413</v>
@@ -34244,7 +34241,7 @@
         <v>79</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L267" t="s" s="2">
         <v>414</v>
@@ -34295,10 +34292,10 @@
       </c>
       <c r="AC267" s="2"/>
       <c r="AD267" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF267" t="s" s="2">
         <v>413</v>
@@ -34333,13 +34330,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D268" t="s" s="2">
         <v>79</v>
@@ -34361,7 +34358,7 @@
         <v>79</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L268" t="s" s="2">
         <v>414</v>
@@ -34452,13 +34449,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D269" t="s" s="2">
         <v>79</v>
@@ -34480,7 +34477,7 @@
         <v>79</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L269" t="s" s="2">
         <v>414</v>
@@ -34571,13 +34568,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D270" t="s" s="2">
         <v>79</v>
@@ -34599,7 +34596,7 @@
         <v>79</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L270" t="s" s="2">
         <v>414</v>
@@ -34690,7 +34687,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>420</v>
@@ -34809,7 +34806,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>428</v>
@@ -34926,13 +34923,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>79</v>
@@ -35043,7 +35040,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>367</v>
@@ -35158,7 +35155,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>368</v>
@@ -35275,7 +35272,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>369</v>
@@ -35394,7 +35391,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>370</v>
@@ -35513,7 +35510,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>376</v>
@@ -35561,7 +35558,7 @@
         <v>79</v>
       </c>
       <c r="S278" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="T278" t="s" s="2">
         <v>79</v>
@@ -35632,7 +35629,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>383</v>
@@ -35749,7 +35746,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>386</v>
@@ -35866,7 +35863,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>391</v>
@@ -35983,7 +35980,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>397</v>
@@ -36102,7 +36099,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>405</v>
@@ -36221,7 +36218,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>413</v>
@@ -36247,7 +36244,7 @@
         <v>79</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L284" t="s" s="2">
         <v>414</v>
@@ -36298,10 +36295,10 @@
       </c>
       <c r="AC284" s="2"/>
       <c r="AD284" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE284" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF284" t="s" s="2">
         <v>413</v>
@@ -36336,13 +36333,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D285" t="s" s="2">
         <v>79</v>
@@ -36364,7 +36361,7 @@
         <v>79</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="L285" t="s" s="2">
         <v>414</v>
@@ -36455,13 +36452,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D286" t="s" s="2">
         <v>79</v>
@@ -36483,7 +36480,7 @@
         <v>79</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L286" t="s" s="2">
         <v>414</v>
@@ -36574,7 +36571,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>420</v>
@@ -36693,7 +36690,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>428</v>
@@ -36810,13 +36807,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D289" t="s" s="2">
         <v>79</v>
@@ -36927,7 +36924,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>367</v>
@@ -37042,7 +37039,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>368</v>
@@ -37159,7 +37156,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>369</v>
@@ -37278,7 +37275,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>370</v>
@@ -37397,7 +37394,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>376</v>
@@ -37445,7 +37442,7 @@
         <v>79</v>
       </c>
       <c r="S294" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="T294" t="s" s="2">
         <v>79</v>
@@ -37516,7 +37513,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>383</v>
@@ -37633,7 +37630,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>386</v>
@@ -37750,7 +37747,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>391</v>
@@ -37867,7 +37864,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>397</v>
@@ -37986,7 +37983,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>405</v>
@@ -38105,7 +38102,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>413</v>
@@ -38131,7 +38128,7 @@
         <v>79</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L300" t="s" s="2">
         <v>414</v>
@@ -38182,10 +38179,10 @@
       </c>
       <c r="AC300" s="2"/>
       <c r="AD300" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE300" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF300" t="s" s="2">
         <v>413</v>
@@ -38220,13 +38217,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D301" t="s" s="2">
         <v>79</v>
@@ -38248,7 +38245,7 @@
         <v>79</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L301" t="s" s="2">
         <v>414</v>
@@ -38339,13 +38336,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D302" t="s" s="2">
         <v>79</v>
@@ -38367,7 +38364,7 @@
         <v>79</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L302" t="s" s="2">
         <v>414</v>
@@ -38458,7 +38455,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>420</v>
@@ -38577,7 +38574,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>428</v>
@@ -38694,13 +38691,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D305" t="s" s="2">
         <v>79</v>
@@ -38811,7 +38808,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>367</v>
@@ -38926,7 +38923,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>368</v>
@@ -39043,7 +39040,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>369</v>
@@ -39162,7 +39159,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>370</v>
@@ -39281,7 +39278,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>376</v>
@@ -39329,7 +39326,7 @@
         <v>79</v>
       </c>
       <c r="S310" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>79</v>
@@ -39400,7 +39397,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>383</v>
@@ -39517,7 +39514,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>386</v>
@@ -39634,7 +39631,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>391</v>
@@ -39751,7 +39748,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>397</v>
@@ -39870,7 +39867,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>405</v>
@@ -39989,7 +39986,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>413</v>
@@ -40106,7 +40103,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>420</v>
@@ -40225,7 +40222,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>428</v>

--- a/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-75-include-immunizationrecommendation-etc/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T11:52:07+00:00</t>
+    <t>2026-02-03T10:09:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -717,7 +717,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1016,7 +1016,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
+Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
